--- a/data/S1960_61_FINAL.xlsx
+++ b/data/S1960_61_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15784,7 +15802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15862,6 +15880,86 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1960_61_0577 'Sokol Hnojice' ROZBITÝ prev CLUB_S1959_60_0593 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0009</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0009 'KVAL  skupina A' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0010</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0010 'KVAL  skupina B' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0011</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0011 'KVAL  skupina C' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0012</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0012 'KVAL  skupina D' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -50019,6 +50117,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0577</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0577 'Sokol Hnojice' ROZBITÝ prev CLUB_S1959_60_0593 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0009</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1960_61_0009 'KVAL  skupina A' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0010</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1960_61_0010 'KVAL  skupina B' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0011</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1960_61_0011 'KVAL  skupina C' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0012</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1960_61_0012 'KVAL  skupina D' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1960_61_FINAL.xlsx
+++ b/data/S1960_61_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>CLUB_S1959_60_0593</t>
+          <t>CLUB_S1959_60_0588</t>
         </is>
       </c>
       <c r="S44" s="3" t="n"/>
@@ -15802,7 +15802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15886,7 +15886,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1960_61_0577 'Sokol Hnojice' ROZBITÝ prev CLUB_S1959_60_0593 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ruda Hvezda Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15896,14 +15896,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1960_61_0009</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0009 'KVAL  skupina A' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15913,14 +15908,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1960_61_0010</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0010 'KVAL  skupina B' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15930,14 +15920,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1960_61_0011</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0011 'KVAL  skupina C' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15947,17 +15932,144 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1960_61_0012</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1960_61_0012 'KVAL  skupina D' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Zliv' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Arma Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1959_60_0588 'Sokol Hnojnice'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1959_60_0598 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -22188,12 +22300,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: city 'Ruda Hvezda Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ruda Hvezda Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -23142,12 +23254,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -23718,12 +23830,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -28537,12 +28649,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -28950,12 +29062,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí.</t>
+          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí. || TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Suchdol</t>
+          <t>Suchdol nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -29338,12 +29450,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -30401,12 +30513,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -30762,12 +30874,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Veselí nL Moravou = Lokomotiva Veselí nL Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). POZOR: NE Veselí nL Lužnicí (Jihocesky). city Veselí nad Moravou. || Veselí nL Lužnicí = TJ Tatran/Prefa Veselí nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Veselí nL Moravou (Jihomoravsky)! Prefa = prefabrikatovy podnik. ČSD = Československá státní dráha. city Veselí nad Lužnicí.</t>
+          <t>Veselí nL Moravou = Lokomotiva Veselí nL Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). POZOR: NE Veselí nL Lužnicí (Jihocesky). city Veselí nad Moravou. || Veselí nL Lužnicí = TJ Tatran/Prefa Veselí nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Veselí nL Moravou (Jihomoravsky)! Prefa = prefabrikatovy podnik. ČSD = Československá státní dráha. city Veselí nad Lužnicí. || TBD: city 'Veselí' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Veselí</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -31239,12 +31351,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí. || Zliv = Tatran Zliv (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceské Budějovice). ZSJ Šamotka = sklenarsky/keramicky podnik. city Zliv.</t>
+          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí. || Zliv = Tatran Zliv (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceské Budějovice). ZSJ Šamotka = sklenarsky/keramicky podnik. city Zliv. || TBD: city 'Zliv' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Zliv</t>
+          <t>Suchdol nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -33674,12 +33786,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Ústí nad Labem podrobny chain (Wiki - registr ustavy 04/2026). **HC Slovan Usti nL Labem** (dnesni nazev): Sokol Ústí nL Labem (1946 zalozeni) -&gt; ZSJ Armaturka Usti nL (1949-1959, podnik Armaturka) -&gt; TJ Chemicka Usti nL (1959-1963) -&gt; 1963 Chemicka ukoncila pro fin.potize -&gt; TJ Slovan Národní výbory (1963+) -&gt; 1966 vyhrali kvalifikaci do II.ligy -&gt; 2003 statutarni mesto Usti vstoupilo majoritou -&gt; 2005/06 vitezstvi 1.ligy -&gt; 2007/08 v Extralize. Patterns: Sokol Usti, Armaturka Usti, Chemicka Usti, Slovan Usti. city Ústí nad Labem.</t>
+          <t>Ústí nad Labem podrobny chain (Wiki - registr ustavy 04/2026). **HC Slovan Usti nL Labem** (dnesni nazev): Sokol Ústí nL Labem (1946 zalozeni) -&gt; ZSJ Armaturka Usti nL (1949-1959, podnik Armaturka) -&gt; TJ Chemicka Usti nL (1959-1963) -&gt; 1963 Chemicka ukoncila pro fin.potize -&gt; TJ Slovan Národní výbory (1963+) -&gt; 1966 vyhrali kvalifikaci do II.ligy -&gt; 2003 statutarni mesto Usti vstoupilo majoritou -&gt; 2005/06 vitezstvi 1.ligy -&gt; 2007/08 v Extralize. Patterns: Sokol Usti, Armaturka Usti, Chemicka Usti, Slovan Usti. city Ústí nad Labem. || TBD: city 'Arma Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Arma Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -35320,12 +35432,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Vsechny hradecke kluby z chain. Genealogie hlavni linie: ZSJ Skoda HK (1949) -&gt; Spartak (1953) -&gt; Stadion HK -&gt; HC Lev HK (1996) -&gt; HC Hradec Kralove -&gt; Mountfield HK. Plus Slavoj HK (drive Slavia HK), Slavoj Třebeš (mestska cast), Nový Hradec Kralove (mestska cast), Sokol Třebeš. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Vsechny hradecke kluby z chain. Genealogie hlavni linie: ZSJ Skoda HK (1949) -&gt; Spartak (1953) -&gt; Stadion HK -&gt; HC Lev HK (1996) -&gt; HC Hradec Kralove -&gt; Mountfield HK. Plus Slavoj HK (drive Slavia HK), Slavoj Třebeš (mestska cast), Nový Hradec Kralove (mestska cast), Sokol Třebeš. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -36071,12 +36183,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -38467,12 +38579,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová.</t>
+          <t>Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová. || TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová</t>
+          <t>Moravská Třebová</t>
         </is>
       </c>
     </row>
@@ -38776,12 +38888,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Horní Staré Město = TJ Jiskra Horní Staré Město (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (mestska cast Trutnova!). NE Stare Mesto u UH (Jihomoravsky), NE Stare Mesto u Sumperka. city Trutnov (Horní Staré Město).</t>
+          <t>Horní Staré Město = TJ Jiskra Horní Staré Město (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (mestska cast Trutnova!). NE Stare Mesto u UH (Jihomoravsky), NE Stare Mesto u Sumperka. city Trutnov (Horní Staré Město). || TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Horní Staré Město</t>
+          <t>Staré Město</t>
         </is>
       </c>
     </row>
@@ -44736,12 +44848,12 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>CLUB_S1959_60_0593</t>
+          <t>CLUB_S1959_60_0588</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Hnojice = Sokol Hnojice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. OLO = Olomouc okres. city Hnojice.</t>
+          <t>Hnojice = Sokol Hnojice (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. OLO = Olomouc okres. city Hnojice. || TBD: auto-prev_club_id (D42/city) → CLUB_S1959_60_0588 'Sokol Hnojnice'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
@@ -50123,11 +50235,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -50172,21 +50284,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1960_61_0577</t>
+          <t>CLUB_S1960_61_0057</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1960_61_0577 'Sokol Hnojice' ROZBITÝ prev CLUB_S1959_60_0593 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Ruda Hvezda Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -50194,21 +50304,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1960_61_0009</t>
+          <t>CLUB_S1960_61_0079</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1960_61_0009 'KVAL  skupina A' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -50216,21 +50324,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1960_61_0010</t>
+          <t>CLUB_S1960_61_0092</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1960_61_0010 'KVAL  skupina B' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -50238,21 +50344,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1960_61_0011</t>
+          <t>CLUB_S1960_61_0205</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1960_61_0011 'KVAL  skupina C' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -50260,24 +50364,242 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1960_61_0012</t>
+          <t>CLUB_S1960_61_0214</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1960_61_0012 'KVAL  skupina D' (L25, parent=NODE_S1960_61_0008) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Suchdol' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0223</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0247</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0255</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0266</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Zliv' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0323</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Arma Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0362</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0380</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0433</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0440</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0577</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1959_60_0588 'Sokol Hnojnice'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1960_61_0579</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1959_60_0598 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1960_61_FINAL.xlsx
+++ b/data/S1960_61_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15802,7 +15802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15982,7 +15982,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Zliv' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Arma Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15994,7 +15994,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Arma Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16018,7 +16018,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1959_60_0588 'Sokol Hnojnice'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16030,46 +16030,10 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1959_60_0598 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1959_60_0588 'Sokol Hnojnice'; ověřit [fix_broken_prev_d42]</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1959_60_0598 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16086,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16145,6 +16109,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16187,6 +16156,11 @@
           <t>12 týmů: základní část (dvoukolově) → finále 1-6 + o udržení 7-12. Mistr: Rudá hvězda Brno. Sestup: Brno ZJŠ, Gottwaldov.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1959_60_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16229,6 +16203,11 @@
           <t>2 skupiny po 12. Kvalifikace o II.ligu tvoří skupiny A-D vítězů krajských přeborů. Oblastní soutěže se ruší po sezoně 1960/61.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1959_60_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16271,6 +16250,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1959_60_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16316,6 +16300,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>TJ Slávia VŠ Bratislava odstoupila po 3. kole; výsledky byly anulovány. Zbytek hráčů přešel do TJ Slovan ÚNV Bratislava "B".</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1959_60_0004</t>
         </is>
       </c>
     </row>
@@ -31351,12 +31340,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí. || Zliv = Tatran Zliv (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceské Budějovice). ZSJ Šamotka = sklenarsky/keramicky podnik. city Zliv. || TBD: city 'Zliv' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Suchdol nL Lužnicí = Tatran Suchdol nL Lužnicí (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). POZOR: vícero Suchdolů. city Suchdol nad Lužnicí. || Zliv = Tatran Zliv (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceské Budějovice). ZSJ Šamotka = sklenarsky/keramicky podnik. city Zliv.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Suchdol nad Lužnicí</t>
+          <t>Zliv</t>
         </is>
       </c>
     </row>
@@ -35432,12 +35421,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Vsechny hradecke kluby z chain. Genealogie hlavni linie: ZSJ Skoda HK (1949) -&gt; Spartak (1953) -&gt; Stadion HK -&gt; HC Lev HK (1996) -&gt; HC Hradec Kralove -&gt; Mountfield HK. Plus Slavoj HK (drive Slavia HK), Slavoj Třebeš (mestska cast), Nový Hradec Kralove (mestska cast), Sokol Třebeš. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Vsechny hradecke kluby z chain. Genealogie hlavni linie: ZSJ Skoda HK (1949) -&gt; Spartak (1953) -&gt; Stadion HK -&gt; HC Lev HK (1996) -&gt; HC Hradec Kralove -&gt; Mountfield HK. Plus Slavoj HK (drive Slavia HK), Slavoj Třebeš (mestska cast), Nový Hradec Kralove (mestska cast), Sokol Třebeš. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -36183,12 +36172,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -50235,7 +50224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -50449,12 +50438,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1960_61_0266</t>
+          <t>CLUB_S1960_61_0323</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Zliv' → 'Suchdol nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Arma Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50469,12 +50458,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1960_61_0323</t>
+          <t>CLUB_S1960_61_0433</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Arma Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50489,12 +50478,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1960_61_0362</t>
+          <t>CLUB_S1960_61_0440</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50509,12 +50498,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1960_61_0380</t>
+          <t>CLUB_S1960_61_0577</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1959_60_0588 'Sokol Hnojnice'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -50529,77 +50518,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1960_61_0433</t>
+          <t>CLUB_S1960_61_0579</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0440</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0577</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1959_60_0588 'Sokol Hnojnice'; ověřit [fix_broken_prev_d42]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CLUB_S1960_61_0579</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1959_60_0598 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1960_61_FINAL.xlsx
+++ b/data/S1960_61_FINAL.xlsx
@@ -847,7 +847,7 @@
         <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M8" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M10" t="n">
         <v>23</v>
@@ -1395,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
         <v>69</v>

--- a/data/S1960_61_FINAL.xlsx
+++ b/data/S1960_61_FINAL.xlsx
@@ -16050,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16112,6 +16112,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1960_61_FINAL.xlsx
+++ b/data/S1960_61_FINAL.xlsx
@@ -16349,6 +16349,16 @@
           <t>NODE_S1960_61_0001</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NODE_S1960_61_0007</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16358,6 +16368,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -16391,6 +16409,8 @@
           <t>NODE_S1960_61_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16400,6 +16420,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -16433,6 +16461,8 @@
           <t>NODE_S1960_61_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16442,6 +16472,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>7.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">

--- a/data/S1960_61_FINAL.xlsx
+++ b/data/S1960_61_FINAL.xlsx
@@ -16409,8 +16409,6 @@
           <t>NODE_S1960_61_0001</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16461,8 +16459,6 @@
           <t>NODE_S1960_61_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
